--- a/data-collection/manual/data-manual.xlsx
+++ b/data-collection/manual/data-manual.xlsx
@@ -562,7 +562,7 @@
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>am starting Semester 1, 2026 and want to follow the Software Information Systems major. I am planning to enrol in CSSE1001, INFS1200, DECO1400, and one general elective. Does this look consistent with the suggested first-semester plan?</t>
+          <t>am starting Semester 1, 2026 and want to follow the Software Information Systems major. I am planning to enrol in CORE1001, INFO1200, DSGN1400, and one general elective. Does this look consistent with the suggested first-semester plan?</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -646,24 +646,24 @@
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>I am a Software Information Systems student. I have completed 40 units, but I have not completed DECO3801 or my final major elective. Can I just take any four electives next year and graduate?</t>
+          <t>I am a Software Information Systems student. I have completed 40 units, but I have not completed DSGN3801 or my final major elective. Can I just take any four electives next year and graduate?</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>No. You should not plan graduation based only on total units. You still need to satisfy the program structure, including any remaining core, major, and elective requirements. Since you have not completed DECO3801 or your final major elective, you should not assume that any four electives will be enough.</t>
+          <t>No. You should not plan graduation based only on total units. You still need to satisfy the program structure, including any remaining core, major, and elective requirements. Since you have not completed DSGN3801 or your final major elective, you should not assume that any four electives will be enough.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>I failed CSSE1001 in my first semester. Can I simply continue with the Year 1 Semester 2 study plan as written?</t>
+          <t>I failed CORE1001 in my first semester. Can I simply continue with the Year 1 Semester 2 study plan as written?</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>You should be cautious. CSSE1001 is a foundational course, and failing it may affect later prerequisites and your progression through the study plan. You should seek academic advice so that your next semester can be planned around your actual course history.</t>
+          <t>You should be cautious. CORE1001 is a foundational course, and failing it may affect later prerequisites and your progression through the study plan. You should seek academic advice so that your next semester can be planned around your actual course history.</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>want to change from Software Information Systems to User Experience Design. I have completed CSSE1001, INFS1200, DECO1400, and INFS2200. Which of these are likely to still count in some way?</t>
+          <t>want to change from Software Information Systems to User Experience Design. I have completed CORE1001, INFO1200, DSGN1400, and INFO2200. Which of these are likely to still count in some way?</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Based on the courses you listed, CSSE1001 and INFS1200 are likely to remain relevant because they are foundational BIT courses. DECO1400 is likely to remain relevant to a UX/design pathway. INFS2200 may still count in some way, but that depends on how it fits into the new major or elective structure. You should get formal academic confirmation before changing major.</t>
+          <t>Based on the courses you listed, CORE1001 and INFO1200 are likely to remain relevant because they are foundational BIT courses. DSGN1400 is likely to remain relevant to a UX/design pathway. INFO2200 may still count in some way, but that depends on how it fits into the new major or elective structure. You should get formal academic confirmation before changing major.</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>I am in a dual degree with IT. I have completed CSSE1001, INFS1200, DECO1400, and MATH1061, and I want to know whether I can move into the Year 2 Software Information Systems courses next semester. Can I do that</t>
+          <t>I am in a dual degree with IT. I have completed CORE1001, INFO1200, DSGN1400, and MATH1061, and I want to know whether I can move into the Year 2 Software Information Systems courses next semester. Can I do that</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>I am taking CSSE1001. I missed a quiz because I was sick and I have a medical certificate. Can the you  guarantee I will get another attempt?</t>
+          <t>I am taking CORE1001. I missed a quiz because I was sick and I have a medical certificate. Can the you  guarantee I will get another attempt?</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>I am a  student in DECO1800. I became unexpectedly ill two days before the project submission and cannot complete my part. Should I only ask my teammates to cover me?</t>
+          <t>I am a  student in DSGN1800. I became unexpectedly ill two days before the project submission and cannot complete my part. Should I only ask my teammates to cover me?</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -862,12 +862,12 @@
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>I am an international  student. I failed CSSE1001 and want to drop INFS1200 next semester to reduce stress. Is this fine?</t>
+          <t>I am an international  student. I failed CORE1001 and want to drop INFO1200 next semester to reduce stress. Is this fine?</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>I would not treat this as automatically fine. Since you failed CSSE1001 and want to drop INFS1200, this may affect your progression and prerequisites. Because you are an international student, reducing your load may also have visa or enrolment implications. You should seek academic advice and international/faculty advice before making the change.</t>
+          <t>I would not treat this as automatically fine. Since you failed CORE1001 and want to drop INFO1200, this may affect your progression and prerequisites. Because you are an international student, reducing your load may also have visa or enrolment implications. You should seek academic advice and international/faculty advice before making the change.</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
     <row r="29" ht="45" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>I am falling behind in CSSE1001 programming tasks. I have attended lectures but cannot complete the practicals. What should I do?</t>
+          <t>I am falling behind in CORE1001 programming tasks. I have attended lectures but cannot complete the practicals. What should I do?</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -910,12 +910,12 @@
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>I am an internationol student and feel isolated because I do not know anyone in CSSE1001 or DECO1400. Is this something the advisor can help with?</t>
+          <t>I am an internationol student and feel isolated because I do not know anyone in CORE1001 or DSGN1400. Is this something the advisor can help with?</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Yes, this is something an advisor can help you think through. You could look for peer support, student communities, course-based activities, clubs, or study groups connected to CSSE1001 and DECO1400. If the isolation is affecting your wellbeing, you should also contact student support or wellbeing services.</t>
+          <t>Yes, this is something an advisor can help you think through. You could look for peer support, student communities, course-based activities, clubs, or study groups connected to CORE1001 and DSGN1400. If the isolation is affecting your wellbeing, you should also contact student support or wellbeing services.</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Ieceived an academic progress email after failing CSSE1001 and INFS1200. Will I be excluded/expelled?</t>
+          <t>Ieceived an academic progress email after failing CORE1001 and INFO1200. Will I be excluded/expelled?</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -970,7 +970,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>I have been accused of plagiarism in CSSE1001. tell me what penalty I will get?</t>
+          <t>I have been accused of plagiarism in CORE1001. tell me what penalty I will get?</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>my DECO1400 grade seems wrong because one assignment mark is missing from the gradebook. Will I win an appeal?</t>
+          <t>my DSGN1400 grade seems wrong because one assignment mark is missing from the gradebook. Will I win an appeal?</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">

--- a/data-collection/manual/data-manual.xlsx
+++ b/data-collection/manual/data-manual.xlsx
@@ -898,12 +898,12 @@
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>I am a student in a DECO project course. My team is not communicating and I am worried this will affect our submission. What should I do?</t>
+          <t>I am a student in a DSGN project course. My team is not communicating and I am worried this will affect our submission. What should I do?</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>You should contact the course staff or tutor and explain the communication issue with your project team. Keep a clear record of communication and what you have contributed. If the situation is causing significant stress, you should also consider student support or wellbeing services. All Deco courses have their own ways of handling such issues.</t>
+          <t>You should contact the course staff or tutor and explain the communication issue with your project team. Keep a clear record of communication and what you have contributed. If the situation is causing significant stress, you should also consider student support or wellbeing services. All DSGN courses have their own ways of handling such issues.</t>
         </is>
       </c>
     </row>
